--- a/data/trans_orig/IQ21A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ21A-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de veces que han estado hospitalizados a lo largo de estos últimos 12 meses</t>
+          <t>Menores según el número de veces que han estado hospitalizados a lo largo de estos últimos 12 meses (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -736,12 +736,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,85</t>
+          <t>1,0; 5,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,38</t>
+          <t>1,0; 3,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,28</t>
+          <t>1,12; 4,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,35</t>
+          <t>1,06; 1,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,53</t>
+          <t>1,06; 1,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -876,17 +876,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,21</t>
+          <t>1,02; 1,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,65</t>
+          <t>1,03; 1,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 15,53</t>
+          <t>1,21; 13,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -896,17 +896,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,17</t>
+          <t>1,03; 1,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,43</t>
+          <t>1,08; 1,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 8,24</t>
+          <t>1,19; 8,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,43</t>
+          <t>1,0; 1,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,44</t>
+          <t>1,0; 1,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,33</t>
+          <t>1,0; 1,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,23</t>
+          <t>1,0; 1,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,26</t>
+          <t>1,05; 1,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,37</t>
+          <t>1,07; 1,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1156,17 +1156,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,76</t>
+          <t>1,06; 1,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,51</t>
+          <t>1,08; 1,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 10,71</t>
+          <t>1,09; 11,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,41</t>
+          <t>1,05; 1,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,23</t>
+          <t>1,16; 5,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">

--- a/data/trans_orig/IQ21A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ21A-Estudios-trans_orig.xlsx
@@ -736,12 +736,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,88</t>
+          <t>1,19; 5,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,39</t>
+          <t>1,0; 3,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,88</t>
+          <t>1,12; 4,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,47</t>
+          <t>1,0; 2,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,34</t>
+          <t>1,06; 1,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,51</t>
+          <t>1,06; 1,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -876,17 +876,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,2</t>
+          <t>1,02; 1,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,64</t>
+          <t>1,03; 1,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 13,2</t>
+          <t>1,08; 14,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,41</t>
+          <t>1,09; 1,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 8,7</t>
+          <t>1,18; 8,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,47</t>
+          <t>1,0; 1,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,45</t>
+          <t>1,0; 1,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,53</t>
+          <t>1,0; 1,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,32</t>
+          <t>1,0; 1,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,34</t>
+          <t>1,0; 1,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,2</t>
+          <t>1,0; 1,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,36</t>
+          <t>1,07; 1,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1156,17 +1156,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,62</t>
+          <t>1,06; 1,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,54</t>
+          <t>1,1; 1,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 11,27</t>
+          <t>1,12; 11,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1176,17 +1176,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,38</t>
+          <t>1,04; 1,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,35</t>
+          <t>1,09; 1,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,86</t>
+          <t>1,15; 6,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
